--- a/光伏配储项目/电价数据/2026/智良站.xlsx
+++ b/光伏配储项目/电价数据/2026/智良站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.5125700000000001</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38473</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7722</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.60065</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.58445</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.5145</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.53034</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43785</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45472</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.42691</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42216</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.81312</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.43344</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.42183</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39661</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38507</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40126</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.4234</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41279</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35418</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39167</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38512</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41715</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39227</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.4209</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41411</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42411</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41211</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44292</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30003</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.32617</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.27445</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29987</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30702</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.31323</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>-0.03785</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>-0.04015999999999999</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>-0.04207</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>-0.03723</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>-0.03348</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>-0.03545</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>-0.02289</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.02562</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.02472</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>-0.049</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.04906</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.01799</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.01321</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>-0.02709</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.01807</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.04363</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>-0.03977</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>-0.04714</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>-0.03775999999999999</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>-0.007809999999999999</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.20026</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.2845299999999999</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.55632</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.42966</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.39902</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.67848</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39574</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.5690599999999999</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43366</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.4376</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.42464</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.5660599999999999</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.4494</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.6039</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.79884</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.62726</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.63152</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.73899</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.9295800000000001</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.41439</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.65964</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.5832999999999999</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.7231599999999999</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.47289</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.37695</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.62393</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.6037</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.50051</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48061</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.44356</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41627</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42599</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.69178</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0.99824</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.63662</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.54569</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.66579</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.49345</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5174500000000001</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50461</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50493</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48684</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.4689</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37887</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37957</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.38993</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33652</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.36971</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35516</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35474</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37404</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.3743</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.3793</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41774</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.48426</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.5515</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.48966</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.42803</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.36617</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34786</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.34848</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42826</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.45138</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.2681</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.24619</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.18958</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.17462</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.30199</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.11018</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.19588</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.37514</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.23537</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.01545</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.16394</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>-0.0399</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.02883</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.00057</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.13606</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.19734</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.1848</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.37452</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>-0.01295</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.02101</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>-0.04199</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.36301</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>-0.03588</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.31865</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.36272</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.37671</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.43623</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.41778</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.45229</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.43302</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.43648</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.42465</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.40244</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.58526</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.48389</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.34342</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.493</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.58786</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.53276</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.6715599999999999</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.63215</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.7194199999999999</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.43759</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.4096</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.76574</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.47147</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.33152</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.46277</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.35441</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.43571</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.44243</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.43575</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42923</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.40349</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.3229</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.3764</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35523</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33471</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.50984</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.3418</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.42754</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.39609</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.42316</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40934</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.37189</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38993</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38379</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36391</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42933</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44502</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33611</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37067</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39649</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.3678</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36858</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36173</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35213</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36715</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35936</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38531</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39637</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47376</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44523</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43953</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34766</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39534</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35307</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36747</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34767</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.26139</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.25287</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.32869</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.20901</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.23385</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.27189</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.32709</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.32195</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34563</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.34315</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.4147</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.32579</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.36829</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.44324</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.41849</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.37239</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.4196</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.44281</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.47323</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.50835</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.41014</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.31387</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.34165</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.34831</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.35571</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.3647</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.45827</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.40832</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.46309</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.39605</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.45192</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.52562</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.37151</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.38135</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.34031</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.35689</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.52561</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.6088600000000001</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.5774600000000001</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.59612</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.46387</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.42261</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.48222</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.40254</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.4474</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.43646</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.4586</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.44416</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.39534</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.37448</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.41984</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.39941</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.39523</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.3987</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36249</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34871</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34207</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.47794</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.35516</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.34211</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38759</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38888</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.39683</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36614</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35804</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38455</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38362</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.3582</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.45013</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35756</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.35996</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35551</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35622</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33635</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33354</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33293</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.32916</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33921</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35152</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38297</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38911</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34511</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.3723</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34308</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39173</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.36214</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.36649</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.34258</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.2609</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34034</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.12481</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.24128</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.19817</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.28232</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.2012</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30437</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.56023</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.32971</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.40198</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.31367</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.21545</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.22822</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.16947</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.10993</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>-0.02186</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.03517</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>-0.00032</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.23859</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.01533</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>-0.02592</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.10203</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.19403</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.19447</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.10228</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.10145</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.10218</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.33624</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.16452</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.32291</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.3218</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.33196</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33791</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.37388</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.36089</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.3536</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.35603</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.39883</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.44607</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.34472</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.39302</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.39221</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.38966</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41511</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.34102</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.35886</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34625</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34057</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31916</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32335</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29368</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.30759</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31554</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31167</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.31608</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.30355</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.34333</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.3822</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35549</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33908</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.31869</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31678</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.31949</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31695</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31395</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31535</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31557</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.30443</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.30457</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.30853</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.30195</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.3063</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31362</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33261</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.30551</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.29999</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.21463</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.22361</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.21544</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.20963</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04474</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.22047</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.21651</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.19464</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.02873</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.1821</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.09617000000000001</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.03304</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.03359</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.03567</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.03774</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.03526</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04226</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04686999999999999</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.04054</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.0408</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.03824</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.04999</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>-0.04616</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>-0.03766</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05797</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.01035</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.03405</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.09595000000000001</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29012</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29181</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31547</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3358</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33592</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.3876</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39195</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38735</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37687</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39932</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39977</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40962</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46715</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35449</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39606</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.39953</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.4167</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35493</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35805</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34473</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35503</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35076</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36797</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.6535</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.39952</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44492</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.4222</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42208</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35969</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35846</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30873</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32256</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35498</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34699</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33483</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.3141600000000001</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.32952</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33451</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32155</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29991</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33513</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33825</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.34954</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34158</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31572</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10252</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04343</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04699</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04481</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.044</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01242</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.21081</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.05155</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04396</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04575</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04563</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04371</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04337</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04550999999999999</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04341</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04527</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04539</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.0436</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04424</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.0145</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04472</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04740999999999999</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04793</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19973</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14271</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28991</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29463</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30451</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.2998</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.2949</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.2928</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29326</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29223</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29675</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29072</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29495</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26873</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29379</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30853</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30372</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.3022</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31432</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31836</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34753</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34424</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36613</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36467</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33528</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33009</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31698</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31033</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40414</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34971</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30701</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31461</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30132</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28112</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29439</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29066</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28081</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27114</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27087</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28101</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17235</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15859</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.1709</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14768</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15942</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15856</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23609</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21398</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22649</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.2688</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28563</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29073</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29067</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28081</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28101</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28041</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27071</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28089</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32233</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31013</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.3049</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31627</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30937</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35893</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29749</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38362</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42819</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45649</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41851</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41535</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38885</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40247</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.2993</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15653</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29438</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31095</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31344</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31274</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34631</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38547</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49798</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9140900000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86252</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29603</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.3533</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.8871599999999999</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63154</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18675</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.86848</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.5356599999999999</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.3305</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03267</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53044</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79069</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5295299999999999</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7726799999999999</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7773099999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87674</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87371</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49287</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.3984</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39953</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44962</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20664</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87882</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55101</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6215000000000001</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53823</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49759</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45577</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42421</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43708</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.4499</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38808</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45267</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41976</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39989</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.3651</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38482</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41453</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43348</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34369</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39004</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33822</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33139</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34459</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.4021</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34727</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45068</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35337</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39985</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.39949</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58536</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42697</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5955499999999999</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60112</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.69001</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46855</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41744</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.58011</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.41662</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.48111</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.35833</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8596200000000001</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.79279</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.8040700000000001</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.26801</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44033</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.3275</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33303</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30563</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.30074</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.54753</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.2672</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31059</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35687</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33271</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33675</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33708</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31786</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30624</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34374</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31509</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32017</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30346</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29555</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31354</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31207</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.3143</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.30981</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31471</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32198</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32291</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35412</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34026</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33796</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33026</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33515</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.4094100000000001</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41204</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45156</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41438</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39106</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37453</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35327</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.91799</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46442</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.42204</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.40759</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.46352</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38026</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.4093</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.36449</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.34853</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34729</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38879</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35887</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34542</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32276</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.39949</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.49897</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35679</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38714</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34322</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35054</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35492</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37025</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35767</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36277</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31634</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31358</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33251</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33782</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31491</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31285</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29063</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31248</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.29076</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.29756</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16624</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30449</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.33198</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.31727</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.30687</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26221</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.1989</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27721</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.19286</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31118</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28327</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31141</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.3117799999999999</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35271</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.11236</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31443</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31143</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31989</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.32132</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.30316</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.3116</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30913</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31399</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29001</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34801</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.2556</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32177</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.33667</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.33718</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27645</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32883</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30982</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.34989</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.3371499999999999</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38519</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.35041</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.44275</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.34975</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.38637</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42315</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35243</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44981</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.33844</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.41988</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35876</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40112</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.39981</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59493</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.34925</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.88962</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.45673</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.16042</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.69977</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79059</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.66415</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5787899999999999</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.44954</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45057</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50093</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.44013</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43734</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41518</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41308</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.4234</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.50015</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41308</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43431</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41257</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43444</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39052</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42763</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.44997</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39641</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42371</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43373</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41308</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41312</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.39994</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42311</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39874</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40232</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.49454</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36281</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.3450299999999999</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29626</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.36657</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.36859</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.34187</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30755</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.31747</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30368</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.55069</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.36371</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.30793</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24965</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.30146</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.15693</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.2784</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27561</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.00945</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.33756</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30118</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26157</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25526</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30715</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28301</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28507</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.29042</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.2918</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.30962</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.3137</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.32387</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31558</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.34001</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.34036</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.40353</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.40023</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35079</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.36028</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.34001</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.36805</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.34126</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36208</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36215</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34887</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.56975</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46194</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.84629</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46417</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43617</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37735</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.45803</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38511</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36816</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33315</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32327</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42147</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33802</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34278</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33762</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32417</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32416</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32296</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32195</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.30853</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31859</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.3146600000000001</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.31828</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.31821</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30912</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32406</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31013</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31627</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.31878</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.38961</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32191</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34825</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39783</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37301</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34863</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33766</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35344</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33353</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.28094</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.28071</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.29457</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.27935</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.22555</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.14159</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.1452</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.27994</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15281</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>-0.01243</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.00851</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14131</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.13616</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.24729</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.13669</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.1835</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.04199</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>-0.00487</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>-0.02148</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.10784</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.10741</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.12634</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.13583</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.14071</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.2764</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.31816</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.3439</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.35559</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.34707</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.36409</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34283</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37906</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34647</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39712</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38391</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.44841</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39876</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.38971</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40046</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39623</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45118</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43839</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.4377200000000001</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44263</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44368</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38982</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39083</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35853</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.3591</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34668</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34815</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3386</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.53692</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.3884</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46744</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42268</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41482</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.36973</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38049</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.37885</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39199</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37927</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36983</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.37998</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39078</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.36995</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.37992</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.34988</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34693</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35484</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.3445</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34488</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33986</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34452</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35442</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.36992</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38001</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32776</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34186</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34862</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.36075</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29791</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31425</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31374</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30853</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29517</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.17956</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.16357</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.04369</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.20072</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30924</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.18111</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.2433</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.04747999999999999</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29612</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28859</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31246</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.35437</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31364</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29398</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.28656</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24221</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31544</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30794</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32591</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30633</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28579</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.32488</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.34155</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33951</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32718</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.32756</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34222</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34516</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.35328</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36687</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.40405</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.38132</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.37191</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.25966</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.34173</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38025</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.3558</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35727</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35473</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41483</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.32021</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36694</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36925</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.35982</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.37969</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38016</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38481</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.3496</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.35983</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.33983</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36546</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41704</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37027</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39077</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35204</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.35939</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.3511</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34123</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34718</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34522</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34909</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34637</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34907</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34263</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34149</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33936</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34023</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.34257</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34953</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36168</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.35223</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33865</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.34042</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33402</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32392</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.30954</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.36392</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.34623</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.39437</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.43493</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.33487</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.4257</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.4745</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.39153</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.3709</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.52596</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24945</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.27405</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.21239</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.2858</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.47482</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.30338</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.32109</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.29563</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.30114</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.31362</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.3108399999999999</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.3103399999999999</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.45846</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.35461</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.35815</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.41495</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.34142</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35285</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.31571</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.40596</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.32565</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.34003</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.43453</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.41679</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.68984</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36218</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.36527</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.32792</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.31858</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.50987</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.22207</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.37886</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30178</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31081</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32602</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.3319</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.31353</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.31247</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.31539</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.32872</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.36057</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32931</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33917</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.33878</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.33485</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.32179</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32752</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.34228</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32663</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32674</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32687</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33001</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32008</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31968</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32285</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32599</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.32974</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33433</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34501</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.33958</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33385</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33899</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.33009</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.33095</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33417</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34342</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.3479100000000001</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32819</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.33237</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.3309</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32445</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.32745</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34111</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.31041</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.18316</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34452</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.21823</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.29887</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.2834</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.30192</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.17688</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.21281</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.23931</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.23994</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33438</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.29952</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.31684</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32732</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.23906</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.30056</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.30586</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.31308</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.31465</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.32745</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36375</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34164</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.3445299999999999</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.3498</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.34979</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.35954</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32972</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.33652</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.33538</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.34332</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.3345</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.33427</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.33569</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.33529</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.36003</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.34474</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.35844</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.34921</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34868</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34948</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.33929</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.33929</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.33997</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.33927</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.33997</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.33997</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.33914</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.33931</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.33936</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.33937</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.33205</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33668</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33929</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.33886</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32421</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.33918</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33636</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.33997</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.33921</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.3392</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33615</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.3398</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32801</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.33927</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33633</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32943</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.21531</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31307</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.08259</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.07625</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.0798</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.08328000000000001</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32547</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.05713</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.05464</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.09852</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.08131000000000001</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.08075</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.08239</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.02503</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.08212</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.08477999999999999</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32974</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.3083399999999999</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.08181000000000001</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.08456</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.21459</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.29877</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33725</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34495</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35864</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.33972</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35514</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.33955</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.33941</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.33867</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.33867</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.33868</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.33869</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.33862</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.34709</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.33844</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.34673</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.34656</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.33311</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.35144</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.34179</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.34526</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.35658</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.35433</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.24088</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45737</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39357</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.33928</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.34051</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.33913</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33946</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.3393</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.37929</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37607</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37058</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36182</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35863</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35786</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35876</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35262</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35589</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35186</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34749</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37019</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35857</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.3563</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37853</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36567</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37966</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35636</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35627</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35098</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35166</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35768</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34927</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32966</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.31926</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33143</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32564</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26553</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.14848</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.07407</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.06737</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.06773</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19987</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.05916</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.27992</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.30943</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28034</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.21643</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.25552</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28497</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.27722</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28946</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.28991</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30438</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32159</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.23047</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29791</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.29285</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34513</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32059</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.33772</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33168</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.33235</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.34752</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.31592</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33336</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.3624</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.34838</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.35964</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31879</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.35771</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.38238</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.3816000000000001</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.37356</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.3752799999999999</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.36955</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.38006</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.37393</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.36698</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.38796</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.38343</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.36227</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.37314</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40023</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.36382</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.35292</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.37215</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.37961</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.37857</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37818</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37461</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36693</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.35981</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34575</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.38592</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.39054</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.38827</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.39101</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.38624</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.3967</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.38636</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.38688</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.38752</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.38736</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.38774</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.38745</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.38739</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.38486</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.36993</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.39006</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38754</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.3896</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.38993</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.38955</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.38963</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.38637</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.38512</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.38907</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.38948</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.3902</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.37248</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.38705</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.37044</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.37277</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.10342</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.4101</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.44665</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.43871</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.17413</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.14025</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.07287</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.08816</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.09759000000000001</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.11555</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.06044</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.2214</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.2314</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.09189</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.00347</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.04592</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.04654</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.08995</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.03472</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.02555</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.10978</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.00852</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.03054</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.03493</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.02165</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.02595</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.02404</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.01675</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.01602</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.04969</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.01267</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.0204</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.24605</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.24755</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.24559</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.34225</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35306</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.35136</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33795</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.37471</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.3985</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.39145</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.43799</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.3782</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.37836</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.38256</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.37845</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.37047</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.40544</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.21956</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.3868</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.38907</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.38625</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.3753</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.37925</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.38851</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.38575</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.39151</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.39183</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.38337</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.38492</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.38296</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41668</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.44644</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42735</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44106</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.44429</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43406</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42401</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44482</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41574</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.39851</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.44396</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39682</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40389</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39583</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38552</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37747</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37256</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35666</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36563</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37399</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37055</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.35964</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35952</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36563</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38556</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.3895</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37918</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36579</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36105</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35482</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.36628</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.36053</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.29301</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.26559</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.30333</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.3006</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.34315</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.28589</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.29124</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.24435</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.08613999999999999</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.02833</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.11048</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.19745</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.10507</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.34024</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.06365</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.04546</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.04769</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.03662</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.03343</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.07298</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.0536</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.08363</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.05454</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.03969</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.03804</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.01971</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.00647</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.07909999999999999</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.07736</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.10726</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.0925</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.24217</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.25301</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.25355</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.26242</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.33392</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.36447</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.3912</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.37029</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.43286</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41573</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41486</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38367</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.37687</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38554</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.39072</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.4087</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40921</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.3454700000000001</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.37104</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37589</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39598</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37878</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35486</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39904</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.37904</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37452</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.35873</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39462</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37975</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36504</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.32863</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44372</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36105</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.39742</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39269</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.3559</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37826</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.3492</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37631</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35596</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35658</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35319</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.34905</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35698</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34524</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34824</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33784</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33016</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.33931</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33416</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.33915</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34413</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.32839</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.32713</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.32701</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33522</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.31689</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.31583</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31305</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.30754</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.25742</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.27575</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.27227</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.2731</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22564</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.2629</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.22987</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.2344</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.24921</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.23021</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.13939</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.26054</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.23816</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.0546</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04304</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25007</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.23425</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.16937</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.24108</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31311</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30121</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.23384</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.23842</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.03922999999999999</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.20677</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.21528</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.19422</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.23295</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.23834</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.19673</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.24054</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.24093</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35253</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.34461</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.31937</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33074</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.38302</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.35415</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.33791</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.35199</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.34638</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.36387</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.35863</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.36839</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34425</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36327</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37801</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.35818</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.35304</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.3578</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34655</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34558</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34684</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.33935</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.34065</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32485</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.3364</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.33997</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34228</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33722</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.32569</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32131</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31669</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.30416</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.30703</v>
+      </c>
+      <c r="N136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.22413</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.21667</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.21669</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.30003</v>
+      </c>
+      <c r="S136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.29613</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.29613</v>
+      </c>
+      <c r="V136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.22374</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.29503</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.29613</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.29652</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.29988</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.27963</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.20556</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.19331</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>-0.04944</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.04945</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04946</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>-0.04987</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.04952</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.04945</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04948</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.03867</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04142</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.03895000000000001</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04828</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04786</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.04720000000000001</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.03856</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.0495</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04948</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04949</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04928</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.00067</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.25238</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04953</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04925</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04949</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.04642</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.02164</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04947</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04945</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03774</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.19017</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.24797</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.2756</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27981</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.30103</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.30475</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.32334</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.21432</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.22631</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.33394</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.21412</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.21282</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.24826</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.22564</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.22568</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.30651</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.30556</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.37926</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.32556</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.32068</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.3012</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.31847</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.29564</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.1389</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.22714</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.5404500000000001</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.22405</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.2666</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.40556</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.32317</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.35103</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.25452</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.33386</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.30391</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.27817</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.31403</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.29222</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.28877</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.28582</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.28914</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.27565</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.29211</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.2705</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.26744</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.29475</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.28429</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.29479</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.29007</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.3348</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.10788</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.34335</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.3107799999999999</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.30514</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.27048</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.26078</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.63098</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.76373</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.75414</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.5809500000000001</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.23438</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.30662</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.02593</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.22692</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.17882</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.20183</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.20104</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.17602</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.05304</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.03909000000000001</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.08459999999999999</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.02318</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.04209</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.0009699999999999999</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.04213</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.00196</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.20982</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.20961</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.01597</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.18145</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.1935</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.18853</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.16186</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25654</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.23634</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.26329</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.27868</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.28305</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.3083</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32497</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33537</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33587</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32914</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35463</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.36686</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.32472</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.3757799999999999</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.3645</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.42399</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.36355</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.36768</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.35277</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.36094</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.3523</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36856</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.35425</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.36441</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.36344</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.32384</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.31958</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32733</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.3281</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32811</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33675</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32152</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.35644</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.29574</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.36592</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.37907</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.37347</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.37391</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.37296</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.35994</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.36118</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.33954</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.34639</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32587</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34178</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.16473</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.33366</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32346</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.32092</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.32734</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.32653</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.33176</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33696</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.34256</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.44614</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.44358</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.37342</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.41499</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.33554</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.32858</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.29872</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.41985</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.41719</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.36086</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.26143</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.26732</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.21259</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.37643</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.09814000000000001</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.05199</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.12505</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.05052</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.08215</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.08891</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.24803</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31142</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14176</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.27685</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.27025</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30545</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.24925</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32595</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.30137</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.32404</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.29496</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.2169</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.24567</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.24276</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.31158</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.31032</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.30059</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.3011</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.3008</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.33575</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.35347</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.35898</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35614</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.35851</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.35859</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.35534</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33577</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34881</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.38196</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36324</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.37811</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.41546</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.40064</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.34806</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.36908</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.35597</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.35623</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.37956</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36272</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.42117</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.33721</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.34414</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.34005</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.44615</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.38775</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.39265</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.35842</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.37461</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.35797</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.35338</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.39372</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.35223</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.37832</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35419</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.34685</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35456</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.33143</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.33325</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33159</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.33805</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36735</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.37593</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36777</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35801</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.36041</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.35662</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.36307</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.3339</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.43592</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.41927</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.28015</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.38042</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.32994</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.36468</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.33026</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.24964</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.24303</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.24837</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.22142</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.30292</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.22539</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.07354999999999999</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.09420000000000001</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.08781</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.24805</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.06448999999999999</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.09329000000000001</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.21629</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.21599</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.21817</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.09282</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.08648</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.09401000000000001</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.09293999999999999</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.09453</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.08497</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.20993</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.10138</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.2628</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.26094</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.30177</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.34649</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.45014</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.34886</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.46832</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.36753</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.3932</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.41514</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.35822</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.45244</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.37161</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.34911</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.37206</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.38221</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.37247</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.41424</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.35388</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.36822</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.36182</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.3915</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.37302</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.36447</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.37626</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.36856</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.2746</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.3376</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.3298</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.33601</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.31621</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.40323</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.37376</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.37466</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.37036</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.34889</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.35887</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.36401</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.36448</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.36517</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.36475</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36184</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.32285</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.33387</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.29897</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35862</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.32506</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.3156</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.32529</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.32314</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.21382</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.32202</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.29945</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.3582</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.29824</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.37153</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.29807</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.10004</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.25653</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.29945</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.25655</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.21384</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.25168</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.24991</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.26479</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.3001</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.44719</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.38995</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.37171</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.24601</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.25011</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.08116</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.2216</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.07614</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.10563</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.10131</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.10174</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.21428</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.24652</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.08495</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33765</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.31548</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.07675</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.09171</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.09622</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.08368</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.22338</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.25838</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.25166</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.24248</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.10358</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.22795</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.27307</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.34132</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.11575</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36866</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.25899</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.31155</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.34349</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.30947</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.39156</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.39209</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.42544</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.44648</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.4409</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.4075</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.42134</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.44856</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.41972</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.45863</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.41558</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.39179</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.45244</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.45374</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.45217</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.42139</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.44509</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.4252</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.37276</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.38831</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.37243</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.3435</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.36349</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.34073</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.3425299999999999</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.23385</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36238</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.34571</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.35885</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.34339</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33247</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.33281</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.29715</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.3428</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.31413</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.3108399999999999</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.32356</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.31366</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.31877</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.24013</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.27602</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.29542</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.08467</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.30261</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.239</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.23824</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.24508</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.30993</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.31155</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.31718</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.32055</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.31167</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.24779</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.29832</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.24419</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.23913</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.25577</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.07844</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.09378</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.2456</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.27401</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.24105</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.22181</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.03814</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.07331</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.2156</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.00571</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.23859</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.05932</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.10597</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.05499</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.02749</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.01865</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.26341</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.03552</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>-0.00245</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.03049</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.04085</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.22998</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.08737</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.01816</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.05088</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.03995</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.04225</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.09343000000000001</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.09647</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.10067</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.09706999999999999</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.26011</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.26201</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.10938</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.11678</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.23116</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.21972</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.24801</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.33281</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.25115</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.26909</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.30874</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.39026</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.38989</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.35542</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.39249</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.36833</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.37781</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.33764</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.35455</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.37446</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.30788</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.36335</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.34282</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.34724</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.24881</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.24736</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.24235</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.2039</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.24242</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.24162</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.5612200000000001</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.32945</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.39355</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.45989</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.3408</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.24318</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.34728</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.32235</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.3702</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.34779</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33886</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.3479</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.34028</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.33568</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.32174</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.31934</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.31308</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.32646</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.24038</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.31715</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.29836</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.33619</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.33745</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.32567</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.31188</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.32135</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.24758</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.24502</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.23877</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.24086</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.09154000000000001</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.09826</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.25553</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.22374</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.23978</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.0537</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.09362999999999999</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.09025</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.3657</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.24812</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.21758</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.04052</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.11768</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.05365</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.0907</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.04988</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>-0.02201</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.0639</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>-0.01237</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.01855</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.11422</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>-0.00367</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.49798</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.2604</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.30556</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.26376</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.25714</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.31701</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.32961</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.30398</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.32454</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.37006</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.35564</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.38222</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36182</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37229</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39033</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36457</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.38196</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.49538</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.37717</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.37515</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.37695</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.38191</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.36132</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.38285</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.34476</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.36036</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.36466</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.24881</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.33952</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35632</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.32051</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.33363</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.30754</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.33925</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.37892</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.37889</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37577</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.37333</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.31631</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.35962</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.29901</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.33658</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.33499</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.34392</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34456</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33858</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33369</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.34605</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.33593</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.34476</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.35261</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34769</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.29907</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.08489000000000001</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.24217</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.21407</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.2404</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.24049</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.07053</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.22081</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.04381</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.02105</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.24507</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.2285</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.23229</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.13585</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.02679</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>-0.00482</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>-0.00065</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>-0.04789</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.02116</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>-0.04599</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>-0.0446</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>-0.00193</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.08708</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.33174</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.14957</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.02022</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.00053</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.31149</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.01084</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.00118</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>-0.01173</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>-0.02088</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.00278</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.22218</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.24664</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.04211</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.22236</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.22257</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.23903</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.2425</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.24097</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.24168</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.25347</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.3322</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.34732</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.34777</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.3474</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.36426</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.37999</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.35533</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37118</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.37997</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.37461</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.38472</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.40152</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.46817</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.38935</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.39057</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.38331</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.38763</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.37083</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.37987</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.3855</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.37727</v>
       </c>
     </row>
   </sheetData>
